--- a/artfynd/A 48128-2023 artfynd.xlsx
+++ b/artfynd/A 48128-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48128-2023 artfynd.xlsx
+++ b/artfynd/A 48128-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1895895</v>
+        <v>91277994</v>
       </c>
       <c r="B2" t="n">
-        <v>89779</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västsura, Vstm</t>
+          <t>Odelbo S, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565846.3989421267</v>
+        <v>565976</v>
       </c>
       <c r="R2" t="n">
-        <v>6619246.451172161</v>
+        <v>6619571</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-03-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-03-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>på torr kvarsittande gren, lågt i kronan.</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,17 +757,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Bryn med barrskog</t>
+          <t>Äldre blandskog</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,12 +789,7 @@
         <v>2594672</v>
       </c>
       <c r="B3" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -856,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565938.1344474821</v>
+        <v>565938</v>
       </c>
       <c r="R3" t="n">
-        <v>6619434.314398152</v>
+        <v>6619434</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,19 +859,9 @@
           <t>2011-05-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-05-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,56 +893,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91277994</v>
+        <v>4429413</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>222133</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Odelbo S, Vstm</t>
+          <t>Västsura ekhage, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565976.1694384542</v>
+        <v>565938</v>
       </c>
       <c r="R4" t="n">
-        <v>6619570.752079121</v>
+        <v>6619434</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,22 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-05-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-05-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,18 +977,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Äldre blandskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Trädbärande naturbetesmark.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 48128-2023 artfynd.xlsx
+++ b/artfynd/A 48128-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91277994</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2594672</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,8 +1012,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4429413</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>